--- a/test_template.xlsx
+++ b/test_template.xlsx
@@ -17,6 +17,7 @@
     <comment ref="A1" authorId="0">
       <text>
         <t xml:space="preserve">Type: date
+Format: dd-mm-yyyy
 Required: YES</t>
       </text>
     </comment>
